--- a/output/yearly_population_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_91_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5337</v>
+        <v>7894</v>
       </c>
       <c r="C2" t="n">
-        <v>6823</v>
+        <v>9691</v>
       </c>
       <c r="D2" t="n">
-        <v>28863</v>
+        <v>20916</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>3702</v>
       </c>
       <c r="C3" t="n">
-        <v>6705</v>
+        <v>3943</v>
       </c>
       <c r="D3" t="n">
-        <v>16100</v>
+        <v>14566</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2743</v>
+        <v>2596</v>
       </c>
       <c r="C4" t="n">
-        <v>5055</v>
+        <v>5336</v>
       </c>
       <c r="D4" t="n">
-        <v>7637</v>
+        <v>7610</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1707</v>
+        <v>1746</v>
       </c>
       <c r="C5" t="n">
-        <v>4047</v>
+        <v>5074</v>
       </c>
       <c r="D5" t="n">
-        <v>2668</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>1077</v>
       </c>
       <c r="C6" t="n">
-        <v>3305</v>
+        <v>3082</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>546</v>
       </c>
       <c r="C7" t="n">
-        <v>1964</v>
+        <v>1640</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>855</v>
+        <v>788</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -898,7 +898,7 @@
         <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6472</v>
+        <v>7862</v>
       </c>
       <c r="C2" t="n">
-        <v>9818</v>
+        <v>14126</v>
       </c>
       <c r="D2" t="n">
-        <v>39500</v>
+        <v>31005</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3699</v>
+        <v>4481</v>
       </c>
       <c r="C3" t="n">
-        <v>5947</v>
+        <v>5769</v>
       </c>
       <c r="D3" t="n">
-        <v>16753</v>
+        <v>14450</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2726</v>
+        <v>2651</v>
       </c>
       <c r="C4" t="n">
-        <v>5741</v>
+        <v>4556</v>
       </c>
       <c r="D4" t="n">
-        <v>8785</v>
+        <v>8513</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1896</v>
+        <v>1868</v>
       </c>
       <c r="C5" t="n">
-        <v>4388</v>
+        <v>5040</v>
       </c>
       <c r="D5" t="n">
-        <v>3324</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>3607</v>
+        <v>3950</v>
       </c>
       <c r="D6" t="n">
-        <v>1306</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>701</v>
       </c>
       <c r="C7" t="n">
-        <v>2535</v>
+        <v>2259</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>1147</v>
       </c>
       <c r="D8" t="n">
         <v>456</v>
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="D9" t="n">
         <v>320</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7220</v>
+        <v>9494</v>
       </c>
       <c r="C2" t="n">
-        <v>12658</v>
+        <v>13425</v>
       </c>
       <c r="D2" t="n">
-        <v>38810</v>
+        <v>31947</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>4757</v>
       </c>
       <c r="C3" t="n">
-        <v>6674</v>
+        <v>8131</v>
       </c>
       <c r="D3" t="n">
-        <v>18410</v>
+        <v>15511</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2684</v>
+        <v>2873</v>
       </c>
       <c r="C4" t="n">
-        <v>5655</v>
+        <v>4941</v>
       </c>
       <c r="D4" t="n">
-        <v>9580</v>
+        <v>9027</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1974</v>
+        <v>1957</v>
       </c>
       <c r="C5" t="n">
-        <v>4868</v>
+        <v>4682</v>
       </c>
       <c r="D5" t="n">
-        <v>4009</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1318</v>
+        <v>1363</v>
       </c>
       <c r="C6" t="n">
-        <v>3854</v>
+        <v>4364</v>
       </c>
       <c r="D6" t="n">
-        <v>1547</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>729</v>
+        <v>825</v>
       </c>
       <c r="C7" t="n">
-        <v>2939</v>
+        <v>2915</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>335</v>
+        <v>407</v>
       </c>
       <c r="C8" t="n">
-        <v>1803</v>
+        <v>1571</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C9" t="n">
-        <v>833</v>
+        <v>765</v>
       </c>
       <c r="D9" t="n">
         <v>330</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6652</v>
+        <v>8658</v>
       </c>
       <c r="C2" t="n">
-        <v>8708</v>
+        <v>9129</v>
       </c>
       <c r="D2" t="n">
-        <v>31931</v>
+        <v>26302</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4758</v>
+        <v>5446</v>
       </c>
       <c r="C3" t="n">
-        <v>10159</v>
+        <v>11456</v>
       </c>
       <c r="D3" t="n">
-        <v>19732</v>
+        <v>16919</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1823</v>
+        <v>1808</v>
       </c>
       <c r="C4" t="n">
-        <v>7767</v>
+        <v>7198</v>
       </c>
       <c r="D4" t="n">
-        <v>9024</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1217</v>
+        <v>1259</v>
       </c>
       <c r="C5" t="n">
-        <v>3776</v>
+        <v>4276</v>
       </c>
       <c r="D5" t="n">
-        <v>2593</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>673</v>
+        <v>762</v>
       </c>
       <c r="C6" t="n">
-        <v>2880</v>
+        <v>2856</v>
       </c>
       <c r="D6" t="n">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
-        <v>1766</v>
+        <v>1539</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>816</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
         <v>323</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4046</v>
+        <v>5160</v>
       </c>
       <c r="C2" t="n">
-        <v>4320</v>
+        <v>4200</v>
       </c>
       <c r="D2" t="n">
-        <v>21827</v>
+        <v>18906</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4804</v>
+        <v>5832</v>
       </c>
       <c r="C3" t="n">
-        <v>8624</v>
+        <v>9443</v>
       </c>
       <c r="D3" t="n">
-        <v>20443</v>
+        <v>17382</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>2732</v>
       </c>
       <c r="C4" t="n">
-        <v>9005</v>
+        <v>9217</v>
       </c>
       <c r="D4" t="n">
-        <v>10378</v>
+        <v>9676</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>5451</v>
+        <v>5598</v>
       </c>
       <c r="D5" t="n">
-        <v>3366</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>893</v>
       </c>
       <c r="C6" t="n">
-        <v>3365</v>
+        <v>3520</v>
       </c>
       <c r="D6" t="n">
-        <v>937</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>2198</v>
+        <v>2007</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>995</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5272</v>
+        <v>5720</v>
       </c>
       <c r="C2" t="n">
-        <v>4188</v>
+        <v>9425</v>
       </c>
       <c r="D2" t="n">
-        <v>19295</v>
+        <v>17774</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3774</v>
+        <v>4665</v>
       </c>
       <c r="C3" t="n">
-        <v>5819</v>
+        <v>6155</v>
       </c>
       <c r="D3" t="n">
-        <v>19257</v>
+        <v>16421</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3021</v>
+        <v>3457</v>
       </c>
       <c r="C4" t="n">
-        <v>8717</v>
+        <v>9135</v>
       </c>
       <c r="D4" t="n">
-        <v>11705</v>
+        <v>10639</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1643</v>
+        <v>1733</v>
       </c>
       <c r="C5" t="n">
-        <v>6975</v>
+        <v>7237</v>
       </c>
       <c r="D5" t="n">
-        <v>4340</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>945</v>
+        <v>1025</v>
       </c>
       <c r="C6" t="n">
-        <v>4253</v>
+        <v>4403</v>
       </c>
       <c r="D6" t="n">
-        <v>1274</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>497</v>
       </c>
       <c r="C7" t="n">
-        <v>2721</v>
+        <v>2678</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>1549</v>
+        <v>1410</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="D9" t="n">
         <v>268</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3145</v>
+        <v>3426</v>
       </c>
       <c r="C2" t="n">
-        <v>1981</v>
+        <v>4392</v>
       </c>
       <c r="D2" t="n">
-        <v>13455</v>
+        <v>12405</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3978</v>
+        <v>4739</v>
       </c>
       <c r="C3" t="n">
-        <v>5094</v>
+        <v>7066</v>
       </c>
       <c r="D3" t="n">
-        <v>18829</v>
+        <v>16193</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3310</v>
+        <v>3798</v>
       </c>
       <c r="C4" t="n">
-        <v>8510</v>
+        <v>8936</v>
       </c>
       <c r="D4" t="n">
-        <v>12605</v>
+        <v>11366</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1795</v>
       </c>
       <c r="C5" t="n">
-        <v>8368</v>
+        <v>8700</v>
       </c>
       <c r="D5" t="n">
-        <v>4599</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>780</v>
+        <v>875</v>
       </c>
       <c r="C6" t="n">
-        <v>5132</v>
+        <v>5269</v>
       </c>
       <c r="D6" t="n">
-        <v>1249</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>2834</v>
+        <v>2711</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1119</v>
+        <v>1033</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3199</v>
+        <v>4575</v>
       </c>
       <c r="C2" t="n">
-        <v>2569</v>
+        <v>5933</v>
       </c>
       <c r="D2" t="n">
-        <v>13121</v>
+        <v>15611</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3099</v>
+        <v>3559</v>
       </c>
       <c r="C3" t="n">
-        <v>3286</v>
+        <v>5216</v>
       </c>
       <c r="D3" t="n">
-        <v>17013</v>
+        <v>14745</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3154</v>
+        <v>3678</v>
       </c>
       <c r="C4" t="n">
-        <v>6807</v>
+        <v>7956</v>
       </c>
       <c r="D4" t="n">
-        <v>13177</v>
+        <v>11761</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2063</v>
+        <v>2276</v>
       </c>
       <c r="C5" t="n">
-        <v>8336</v>
+        <v>8706</v>
       </c>
       <c r="D5" t="n">
-        <v>5612</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>1112</v>
       </c>
       <c r="C6" t="n">
-        <v>6471</v>
+        <v>6689</v>
       </c>
       <c r="D6" t="n">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>3789</v>
+        <v>3765</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1745</v>
+        <v>1644</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2194</v>
+        <v>3129</v>
       </c>
       <c r="C2" t="n">
-        <v>2032</v>
+        <v>3260</v>
       </c>
       <c r="D2" t="n">
-        <v>10248</v>
+        <v>11539</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2743</v>
+        <v>3397</v>
       </c>
       <c r="C3" t="n">
-        <v>2733</v>
+        <v>5042</v>
       </c>
       <c r="D3" t="n">
-        <v>15783</v>
+        <v>14188</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2888</v>
+        <v>3323</v>
       </c>
       <c r="C4" t="n">
-        <v>5441</v>
+        <v>6864</v>
       </c>
       <c r="D4" t="n">
-        <v>13381</v>
+        <v>11888</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2268</v>
+        <v>2540</v>
       </c>
       <c r="C5" t="n">
-        <v>7939</v>
+        <v>8592</v>
       </c>
       <c r="D5" t="n">
-        <v>6294</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1182</v>
+        <v>1307</v>
       </c>
       <c r="C6" t="n">
-        <v>7300</v>
+        <v>7572</v>
       </c>
       <c r="D6" t="n">
-        <v>2051</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>4678</v>
+        <v>4709</v>
       </c>
       <c r="D7" t="n">
-        <v>727</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2225</v>
+        <v>2125</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>627</v>
+        <v>599</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3322</v>
+        <v>4495</v>
       </c>
       <c r="C2" t="n">
-        <v>7673</v>
+        <v>10360</v>
       </c>
       <c r="D2" t="n">
-        <v>11700</v>
+        <v>19933</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2150</v>
+        <v>2782</v>
       </c>
       <c r="C3" t="n">
-        <v>2184</v>
+        <v>3906</v>
       </c>
       <c r="D3" t="n">
-        <v>14108</v>
+        <v>12962</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2466</v>
+        <v>2909</v>
       </c>
       <c r="C4" t="n">
-        <v>4183</v>
+        <v>5969</v>
       </c>
       <c r="D4" t="n">
-        <v>13320</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2257</v>
+        <v>2577</v>
       </c>
       <c r="C5" t="n">
-        <v>6766</v>
+        <v>7733</v>
       </c>
       <c r="D5" t="n">
-        <v>7055</v>
+        <v>6535</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1585</v>
       </c>
       <c r="C6" t="n">
-        <v>7484</v>
+        <v>7891</v>
       </c>
       <c r="D6" t="n">
-        <v>2554</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>536</v>
       </c>
       <c r="C7" t="n">
-        <v>5698</v>
+        <v>5745</v>
       </c>
       <c r="D7" t="n">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>3065</v>
+        <v>3031</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1149</v>
+        <v>1077</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>7417</v>
       </c>
       <c r="C2" t="n">
-        <v>4747</v>
+        <v>5376</v>
       </c>
       <c r="D2" t="n">
-        <v>7781</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2402</v>
+        <v>3250</v>
       </c>
       <c r="C2" t="n">
-        <v>4419</v>
+        <v>6050</v>
       </c>
       <c r="D2" t="n">
-        <v>8705</v>
+        <v>14830</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2895</v>
+        <v>3696</v>
       </c>
       <c r="C3" t="n">
-        <v>3605</v>
+        <v>5650</v>
       </c>
       <c r="D3" t="n">
-        <v>15093</v>
+        <v>14356</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3346</v>
+        <v>3845</v>
       </c>
       <c r="C4" t="n">
-        <v>6368</v>
+        <v>8591</v>
       </c>
       <c r="D4" t="n">
-        <v>13585</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
-        <v>10219</v>
+        <v>11163</v>
       </c>
       <c r="D5" t="n">
-        <v>6331</v>
+        <v>5947</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="C6" t="n">
-        <v>7050</v>
+        <v>7099</v>
       </c>
       <c r="D6" t="n">
-        <v>1997</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>3003</v>
+        <v>2970</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1126</v>
+        <v>1055</v>
       </c>
       <c r="D8" t="n">
         <v>294</v>
@@ -4302,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6314</v>
+        <v>7531</v>
       </c>
       <c r="C2" t="n">
-        <v>8005</v>
+        <v>7005</v>
       </c>
       <c r="D2" t="n">
-        <v>9895</v>
+        <v>13502</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2198</v>
+        <v>3150</v>
       </c>
       <c r="C3" t="n">
-        <v>2430</v>
+        <v>2752</v>
       </c>
       <c r="D3" t="n">
-        <v>1946</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3916</v>
+        <v>4764</v>
       </c>
       <c r="C2" t="n">
-        <v>8684</v>
+        <v>4567</v>
       </c>
       <c r="D2" t="n">
-        <v>15875</v>
+        <v>22692</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3493</v>
+        <v>4387</v>
       </c>
       <c r="C3" t="n">
-        <v>4856</v>
+        <v>4448</v>
       </c>
       <c r="D3" t="n">
-        <v>3138</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>988</v>
+        <v>1402</v>
       </c>
       <c r="C4" t="n">
+        <v>1655</v>
+      </c>
+      <c r="D4" t="n">
         <v>1490</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1573</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4983</v>
+        <v>4649</v>
       </c>
       <c r="C2" t="n">
-        <v>7834</v>
+        <v>6489</v>
       </c>
       <c r="D2" t="n">
-        <v>28769</v>
+        <v>30776</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3052</v>
+        <v>3773</v>
       </c>
       <c r="C3" t="n">
-        <v>6010</v>
+        <v>3906</v>
       </c>
       <c r="D3" t="n">
-        <v>4949</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1895</v>
+        <v>2452</v>
       </c>
       <c r="C4" t="n">
-        <v>3365</v>
+        <v>3202</v>
       </c>
       <c r="D4" t="n">
-        <v>1825</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>466</v>
+        <v>635</v>
       </c>
       <c r="C5" t="n">
-        <v>908</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5615</v>
+        <v>4798</v>
       </c>
       <c r="C2" t="n">
-        <v>5155</v>
+        <v>11971</v>
       </c>
       <c r="D2" t="n">
-        <v>41279</v>
+        <v>34347</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3251</v>
+        <v>3451</v>
       </c>
       <c r="C3" t="n">
-        <v>6048</v>
+        <v>4556</v>
       </c>
       <c r="D3" t="n">
-        <v>8221</v>
+        <v>9551</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2110</v>
+        <v>2659</v>
       </c>
       <c r="C4" t="n">
-        <v>4684</v>
+        <v>3513</v>
       </c>
       <c r="D4" t="n">
-        <v>2339</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>967</v>
+        <v>1268</v>
       </c>
       <c r="C5" t="n">
-        <v>2186</v>
+        <v>2111</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5918</v>
+        <v>5840</v>
       </c>
       <c r="C2" t="n">
-        <v>5357</v>
+        <v>8943</v>
       </c>
       <c r="D2" t="n">
-        <v>31346</v>
+        <v>29439</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3193</v>
+        <v>2988</v>
       </c>
       <c r="C3" t="n">
-        <v>4580</v>
+        <v>6836</v>
       </c>
       <c r="D3" t="n">
-        <v>11915</v>
+        <v>11898</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1652</v>
+        <v>1886</v>
       </c>
       <c r="C4" t="n">
-        <v>4452</v>
+        <v>3348</v>
       </c>
       <c r="D4" t="n">
-        <v>2916</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>808</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="n">
-        <v>2531</v>
+        <v>2057</v>
       </c>
       <c r="D5" t="n">
-        <v>1135</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6040</v>
+        <v>5337</v>
       </c>
       <c r="C2" t="n">
-        <v>9160</v>
+        <v>4684</v>
       </c>
       <c r="D2" t="n">
-        <v>27270</v>
+        <v>23540</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3787</v>
+        <v>3672</v>
       </c>
       <c r="C3" t="n">
-        <v>4326</v>
+        <v>6935</v>
       </c>
       <c r="D3" t="n">
-        <v>14302</v>
+        <v>13969</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="C4" t="n">
-        <v>4436</v>
+        <v>5387</v>
       </c>
       <c r="D4" t="n">
-        <v>4613</v>
+        <v>4893</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1098</v>
+        <v>1306</v>
       </c>
       <c r="C5" t="n">
-        <v>3578</v>
+        <v>2750</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>505</v>
+        <v>648</v>
       </c>
       <c r="C6" t="n">
-        <v>1846</v>
+        <v>1569</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
         <v>281</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5310</v>
+        <v>5485</v>
       </c>
       <c r="C2" t="n">
-        <v>9362</v>
+        <v>4079</v>
       </c>
       <c r="D2" t="n">
-        <v>27911</v>
+        <v>21919</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4013</v>
+        <v>3687</v>
       </c>
       <c r="C3" t="n">
-        <v>6026</v>
+        <v>4940</v>
       </c>
       <c r="D3" t="n">
-        <v>15347</v>
+        <v>14494</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2525</v>
+        <v>2479</v>
       </c>
       <c r="C4" t="n">
-        <v>4281</v>
+        <v>6151</v>
       </c>
       <c r="D4" t="n">
-        <v>6333</v>
+        <v>6486</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1525</v>
       </c>
       <c r="C5" t="n">
-        <v>3973</v>
+        <v>4135</v>
       </c>
       <c r="D5" t="n">
-        <v>1975</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>728</v>
+        <v>890</v>
       </c>
       <c r="C6" t="n">
-        <v>2721</v>
+        <v>2159</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>378</v>
       </c>
       <c r="C7" t="n">
-        <v>1290</v>
+        <v>1144</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_91_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7894</v>
+        <v>4394</v>
       </c>
       <c r="C2" t="n">
-        <v>9691</v>
+        <v>6229</v>
       </c>
       <c r="D2" t="n">
-        <v>20916</v>
+        <v>26686</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3702</v>
+        <v>2873</v>
       </c>
       <c r="C3" t="n">
-        <v>3943</v>
+        <v>6139</v>
       </c>
       <c r="D3" t="n">
-        <v>14566</v>
+        <v>11212</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2596</v>
+        <v>2385</v>
       </c>
       <c r="C4" t="n">
-        <v>5336</v>
+        <v>6402</v>
       </c>
       <c r="D4" t="n">
-        <v>7610</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1746</v>
+        <v>1595</v>
       </c>
       <c r="C5" t="n">
-        <v>5074</v>
+        <v>4595</v>
       </c>
       <c r="D5" t="n">
-        <v>2794</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1077</v>
+        <v>921</v>
       </c>
       <c r="C6" t="n">
-        <v>3082</v>
+        <v>3271</v>
       </c>
       <c r="D6" t="n">
-        <v>1112</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>546</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>1640</v>
+        <v>2305</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>788</v>
+        <v>1273</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>522</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7862</v>
+        <v>5272</v>
       </c>
       <c r="C2" t="n">
-        <v>14126</v>
+        <v>8386</v>
       </c>
       <c r="D2" t="n">
-        <v>31005</v>
+        <v>24041</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4481</v>
+        <v>2885</v>
       </c>
       <c r="C3" t="n">
-        <v>5769</v>
+        <v>5447</v>
       </c>
       <c r="D3" t="n">
-        <v>14450</v>
+        <v>12563</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2651</v>
+        <v>2222</v>
       </c>
       <c r="C4" t="n">
-        <v>4556</v>
+        <v>6083</v>
       </c>
       <c r="D4" t="n">
-        <v>8513</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1868</v>
+        <v>1711</v>
       </c>
       <c r="C5" t="n">
-        <v>5040</v>
+        <v>5332</v>
       </c>
       <c r="D5" t="n">
-        <v>3421</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>1110</v>
       </c>
       <c r="C6" t="n">
-        <v>3950</v>
+        <v>3792</v>
       </c>
       <c r="D6" t="n">
-        <v>1355</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>701</v>
+        <v>572</v>
       </c>
       <c r="C7" t="n">
-        <v>2259</v>
+        <v>2707</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="C8" t="n">
-        <v>1147</v>
+        <v>1717</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>825</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9494</v>
+        <v>5928</v>
       </c>
       <c r="C2" t="n">
-        <v>13425</v>
+        <v>7397</v>
       </c>
       <c r="D2" t="n">
-        <v>31947</v>
+        <v>24434</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4757</v>
+        <v>3126</v>
       </c>
       <c r="C3" t="n">
-        <v>8131</v>
+        <v>5894</v>
       </c>
       <c r="D3" t="n">
-        <v>15511</v>
+        <v>13136</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2873</v>
+        <v>2145</v>
       </c>
       <c r="C4" t="n">
-        <v>4941</v>
+        <v>5623</v>
       </c>
       <c r="D4" t="n">
-        <v>9027</v>
+        <v>6682</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1957</v>
+        <v>1709</v>
       </c>
       <c r="C5" t="n">
-        <v>4682</v>
+        <v>5538</v>
       </c>
       <c r="D5" t="n">
-        <v>4017</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1363</v>
+        <v>1230</v>
       </c>
       <c r="C6" t="n">
-        <v>4364</v>
+        <v>4342</v>
       </c>
       <c r="D6" t="n">
-        <v>1634</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>825</v>
+        <v>702</v>
       </c>
       <c r="C7" t="n">
-        <v>2915</v>
+        <v>3115</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>407</v>
+        <v>325</v>
       </c>
       <c r="C8" t="n">
-        <v>1571</v>
+        <v>2104</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>765</v>
+        <v>1148</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>518</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8658</v>
+        <v>5441</v>
       </c>
       <c r="C2" t="n">
-        <v>9129</v>
+        <v>5029</v>
       </c>
       <c r="D2" t="n">
-        <v>26302</v>
+        <v>20177</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5446</v>
+        <v>3798</v>
       </c>
       <c r="C3" t="n">
-        <v>11456</v>
+        <v>8867</v>
       </c>
       <c r="D3" t="n">
-        <v>16919</v>
+        <v>14032</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1808</v>
+        <v>1579</v>
       </c>
       <c r="C4" t="n">
-        <v>7198</v>
+        <v>8393</v>
       </c>
       <c r="D4" t="n">
-        <v>8669</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1259</v>
+        <v>1136</v>
       </c>
       <c r="C5" t="n">
-        <v>4276</v>
+        <v>4255</v>
       </c>
       <c r="D5" t="n">
-        <v>2681</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>762</v>
+        <v>648</v>
       </c>
       <c r="C6" t="n">
-        <v>2856</v>
+        <v>3052</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1539</v>
+        <v>2061</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>749</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5160</v>
+        <v>3361</v>
       </c>
       <c r="C2" t="n">
-        <v>4200</v>
+        <v>2818</v>
       </c>
       <c r="D2" t="n">
-        <v>18906</v>
+        <v>14314</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5832</v>
+        <v>3876</v>
       </c>
       <c r="C3" t="n">
-        <v>9443</v>
+        <v>6478</v>
       </c>
       <c r="D3" t="n">
-        <v>17382</v>
+        <v>14059</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2732</v>
+        <v>2109</v>
       </c>
       <c r="C4" t="n">
-        <v>9217</v>
+        <v>8678</v>
       </c>
       <c r="D4" t="n">
-        <v>9676</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>5598</v>
+        <v>6078</v>
       </c>
       <c r="D5" t="n">
-        <v>3398</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>3520</v>
+        <v>3653</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>2007</v>
+        <v>2483</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>995</v>
+        <v>1452</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>556</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5720</v>
+        <v>3569</v>
       </c>
       <c r="C2" t="n">
-        <v>9425</v>
+        <v>8992</v>
       </c>
       <c r="D2" t="n">
-        <v>17774</v>
+        <v>12554</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4665</v>
+        <v>3071</v>
       </c>
       <c r="C3" t="n">
-        <v>6155</v>
+        <v>4219</v>
       </c>
       <c r="D3" t="n">
-        <v>16421</v>
+        <v>13263</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3457</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>9135</v>
+        <v>7420</v>
       </c>
       <c r="D4" t="n">
-        <v>10639</v>
+        <v>8356</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1733</v>
+        <v>1439</v>
       </c>
       <c r="C5" t="n">
-        <v>7237</v>
+        <v>7174</v>
       </c>
       <c r="D5" t="n">
-        <v>4259</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1025</v>
+        <v>889</v>
       </c>
       <c r="C6" t="n">
-        <v>4403</v>
+        <v>4747</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>2678</v>
+        <v>3010</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>1410</v>
+        <v>1879</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>618</v>
+        <v>894</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
         <v>214</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3426</v>
+        <v>2106</v>
       </c>
       <c r="C2" t="n">
-        <v>4392</v>
+        <v>4196</v>
       </c>
       <c r="D2" t="n">
-        <v>12405</v>
+        <v>8762</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4739</v>
+        <v>3078</v>
       </c>
       <c r="C3" t="n">
-        <v>7066</v>
+        <v>5694</v>
       </c>
       <c r="D3" t="n">
-        <v>16193</v>
+        <v>12892</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3798</v>
+        <v>2747</v>
       </c>
       <c r="C4" t="n">
-        <v>8936</v>
+        <v>6933</v>
       </c>
       <c r="D4" t="n">
-        <v>11366</v>
+        <v>8958</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>1523</v>
       </c>
       <c r="C5" t="n">
-        <v>8700</v>
+        <v>8273</v>
       </c>
       <c r="D5" t="n">
-        <v>4493</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>875</v>
+        <v>748</v>
       </c>
       <c r="C6" t="n">
-        <v>5269</v>
+        <v>5776</v>
       </c>
       <c r="D6" t="n">
-        <v>1265</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2711</v>
+        <v>3276</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>1446</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4575</v>
+        <v>2302</v>
       </c>
       <c r="C2" t="n">
-        <v>5933</v>
+        <v>9110</v>
       </c>
       <c r="D2" t="n">
-        <v>15611</v>
+        <v>13205</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3559</v>
+        <v>2281</v>
       </c>
       <c r="C3" t="n">
-        <v>5216</v>
+        <v>4445</v>
       </c>
       <c r="D3" t="n">
-        <v>14745</v>
+        <v>11463</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3678</v>
+        <v>2546</v>
       </c>
       <c r="C4" t="n">
-        <v>7956</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>11761</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2276</v>
+        <v>1799</v>
       </c>
       <c r="C5" t="n">
-        <v>8706</v>
+        <v>7575</v>
       </c>
       <c r="D5" t="n">
-        <v>5346</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1112</v>
+        <v>954</v>
       </c>
       <c r="C6" t="n">
-        <v>6689</v>
+        <v>6834</v>
       </c>
       <c r="D6" t="n">
-        <v>1682</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>3765</v>
+        <v>4343</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1644</v>
+        <v>2137</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>523</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3129</v>
+        <v>1563</v>
       </c>
       <c r="C2" t="n">
-        <v>3260</v>
+        <v>4699</v>
       </c>
       <c r="D2" t="n">
-        <v>11539</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3397</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="n">
-        <v>5042</v>
+        <v>5711</v>
       </c>
       <c r="D3" t="n">
-        <v>14188</v>
+        <v>11048</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3323</v>
+        <v>2253</v>
       </c>
       <c r="C4" t="n">
-        <v>6864</v>
+        <v>5560</v>
       </c>
       <c r="D4" t="n">
-        <v>11888</v>
+        <v>9420</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2540</v>
+        <v>1945</v>
       </c>
       <c r="C5" t="n">
-        <v>8592</v>
+        <v>7228</v>
       </c>
       <c r="D5" t="n">
-        <v>5912</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1307</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="n">
-        <v>7572</v>
+        <v>7350</v>
       </c>
       <c r="D6" t="n">
-        <v>2027</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>4709</v>
+        <v>5249</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2125</v>
+        <v>2698</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>827</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4495</v>
+        <v>3161</v>
       </c>
       <c r="C2" t="n">
-        <v>10360</v>
+        <v>12407</v>
       </c>
       <c r="D2" t="n">
-        <v>19933</v>
+        <v>9257</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2782</v>
+        <v>1565</v>
       </c>
       <c r="C3" t="n">
-        <v>3906</v>
+        <v>4761</v>
       </c>
       <c r="D3" t="n">
-        <v>12962</v>
+        <v>10213</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2909</v>
+        <v>1887</v>
       </c>
       <c r="C4" t="n">
-        <v>5969</v>
+        <v>5454</v>
       </c>
       <c r="D4" t="n">
-        <v>11857</v>
+        <v>9368</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2577</v>
+        <v>1892</v>
       </c>
       <c r="C5" t="n">
-        <v>7733</v>
+        <v>6389</v>
       </c>
       <c r="D5" t="n">
-        <v>6535</v>
+        <v>5283</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1585</v>
+        <v>1284</v>
       </c>
       <c r="C6" t="n">
-        <v>7891</v>
+        <v>7310</v>
       </c>
       <c r="D6" t="n">
-        <v>2485</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>5745</v>
+        <v>6029</v>
       </c>
       <c r="D7" t="n">
-        <v>878</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3031</v>
+        <v>3596</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1077</v>
+        <v>1458</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7417</v>
+        <v>4397</v>
       </c>
       <c r="C2" t="n">
-        <v>5376</v>
+        <v>14041</v>
       </c>
       <c r="D2" t="n">
-        <v>5341</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3250</v>
+        <v>2258</v>
       </c>
       <c r="C2" t="n">
-        <v>6050</v>
+        <v>7048</v>
       </c>
       <c r="D2" t="n">
-        <v>14830</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3696</v>
+        <v>2206</v>
       </c>
       <c r="C3" t="n">
-        <v>5650</v>
+        <v>6946</v>
       </c>
       <c r="D3" t="n">
-        <v>14356</v>
+        <v>11026</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3845</v>
+        <v>2708</v>
       </c>
       <c r="C4" t="n">
-        <v>8591</v>
+        <v>7701</v>
       </c>
       <c r="D4" t="n">
-        <v>12154</v>
+        <v>9631</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1512</v>
+        <v>1238</v>
       </c>
       <c r="C5" t="n">
-        <v>11163</v>
+        <v>9901</v>
       </c>
       <c r="D5" t="n">
-        <v>5947</v>
+        <v>4799</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="C6" t="n">
-        <v>7099</v>
+        <v>7341</v>
       </c>
       <c r="D6" t="n">
-        <v>1941</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>2970</v>
+        <v>3524</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1055</v>
+        <v>1428</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7531</v>
+        <v>6553</v>
       </c>
       <c r="C2" t="n">
-        <v>7005</v>
+        <v>6822</v>
       </c>
       <c r="D2" t="n">
-        <v>13502</v>
+        <v>9596</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3150</v>
+        <v>1869</v>
       </c>
       <c r="C3" t="n">
-        <v>2752</v>
+        <v>7076</v>
       </c>
       <c r="D3" t="n">
-        <v>1536</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4764</v>
+        <v>5068</v>
       </c>
       <c r="C2" t="n">
-        <v>4567</v>
+        <v>4223</v>
       </c>
       <c r="D2" t="n">
-        <v>22692</v>
+        <v>20243</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4387</v>
+        <v>3453</v>
       </c>
       <c r="C3" t="n">
-        <v>4448</v>
+        <v>5978</v>
       </c>
       <c r="D3" t="n">
-        <v>3433</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1402</v>
+        <v>846</v>
       </c>
       <c r="C4" t="n">
-        <v>1655</v>
+        <v>4189</v>
       </c>
       <c r="D4" t="n">
-        <v>1490</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4649</v>
+        <v>4328</v>
       </c>
       <c r="C2" t="n">
-        <v>6489</v>
+        <v>5955</v>
       </c>
       <c r="D2" t="n">
-        <v>30776</v>
+        <v>17201</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3773</v>
+        <v>3487</v>
       </c>
       <c r="C3" t="n">
-        <v>3906</v>
+        <v>4369</v>
       </c>
       <c r="D3" t="n">
-        <v>6267</v>
+        <v>5629</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2452</v>
+        <v>1823</v>
       </c>
       <c r="C4" t="n">
-        <v>3202</v>
+        <v>5057</v>
       </c>
       <c r="D4" t="n">
-        <v>1817</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>635</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>2386</v>
       </c>
       <c r="D5" t="n">
-        <v>1194</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>176</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4798</v>
+        <v>4762</v>
       </c>
       <c r="C2" t="n">
-        <v>11971</v>
+        <v>6839</v>
       </c>
       <c r="D2" t="n">
-        <v>34347</v>
+        <v>17991</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3451</v>
+        <v>3197</v>
       </c>
       <c r="C3" t="n">
-        <v>4556</v>
+        <v>4513</v>
       </c>
       <c r="D3" t="n">
-        <v>9551</v>
+        <v>6991</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2659</v>
+        <v>2220</v>
       </c>
       <c r="C4" t="n">
-        <v>3513</v>
+        <v>4581</v>
       </c>
       <c r="D4" t="n">
-        <v>2573</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1268</v>
+        <v>910</v>
       </c>
       <c r="C5" t="n">
-        <v>2111</v>
+        <v>3721</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>653</v>
+        <v>1337</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5840</v>
+        <v>5287</v>
       </c>
       <c r="C2" t="n">
-        <v>8943</v>
+        <v>10558</v>
       </c>
       <c r="D2" t="n">
-        <v>29439</v>
+        <v>15858</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2988</v>
+        <v>2878</v>
       </c>
       <c r="C3" t="n">
-        <v>6836</v>
+        <v>4655</v>
       </c>
       <c r="D3" t="n">
-        <v>11898</v>
+        <v>7687</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1886</v>
+        <v>1683</v>
       </c>
       <c r="C4" t="n">
-        <v>3348</v>
+        <v>3682</v>
       </c>
       <c r="D4" t="n">
-        <v>3290</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1034</v>
+        <v>804</v>
       </c>
       <c r="C5" t="n">
-        <v>2057</v>
+        <v>3036</v>
       </c>
       <c r="D5" t="n">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>376</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>934</v>
+        <v>1685</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>533</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5337</v>
+        <v>4745</v>
       </c>
       <c r="C2" t="n">
-        <v>4684</v>
+        <v>9653</v>
       </c>
       <c r="D2" t="n">
-        <v>23540</v>
+        <v>17228</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3672</v>
+        <v>3394</v>
       </c>
       <c r="C3" t="n">
-        <v>6935</v>
+        <v>6974</v>
       </c>
       <c r="D3" t="n">
-        <v>13969</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2136</v>
+        <v>2002</v>
       </c>
       <c r="C4" t="n">
-        <v>5387</v>
+        <v>4193</v>
       </c>
       <c r="D4" t="n">
-        <v>4893</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>1110</v>
       </c>
       <c r="C5" t="n">
-        <v>2750</v>
+        <v>3351</v>
       </c>
       <c r="D5" t="n">
-        <v>1553</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>648</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>1569</v>
+        <v>2413</v>
       </c>
       <c r="D6" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>667</v>
+        <v>1187</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>392</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5485</v>
+        <v>3642</v>
       </c>
       <c r="C2" t="n">
-        <v>4079</v>
+        <v>6749</v>
       </c>
       <c r="D2" t="n">
-        <v>21919</v>
+        <v>27136</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3687</v>
+        <v>3334</v>
       </c>
       <c r="C3" t="n">
-        <v>4940</v>
+        <v>7301</v>
       </c>
       <c r="D3" t="n">
-        <v>14494</v>
+        <v>9279</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2479</v>
+        <v>2320</v>
       </c>
       <c r="C4" t="n">
-        <v>6151</v>
+        <v>5680</v>
       </c>
       <c r="D4" t="n">
-        <v>6486</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>1355</v>
       </c>
       <c r="C5" t="n">
-        <v>4135</v>
+        <v>3742</v>
       </c>
       <c r="D5" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>890</v>
+        <v>726</v>
       </c>
       <c r="C6" t="n">
-        <v>2159</v>
+        <v>2880</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>1144</v>
+        <v>1811</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>474</v>
+        <v>796</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_91_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4394</v>
+        <v>1252</v>
       </c>
       <c r="C2" t="n">
-        <v>6229</v>
+        <v>3060</v>
       </c>
       <c r="D2" t="n">
-        <v>26686</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2873</v>
+        <v>1988</v>
       </c>
       <c r="C3" t="n">
-        <v>6139</v>
+        <v>6936</v>
       </c>
       <c r="D3" t="n">
-        <v>11212</v>
+        <v>15130</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2385</v>
+        <v>1101</v>
       </c>
       <c r="C4" t="n">
-        <v>6402</v>
+        <v>7549</v>
       </c>
       <c r="D4" t="n">
-        <v>5137</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>4595</v>
+        <v>3712</v>
       </c>
       <c r="D5" t="n">
-        <v>2209</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>921</v>
+        <v>232</v>
       </c>
       <c r="C6" t="n">
-        <v>3271</v>
+        <v>1161</v>
       </c>
       <c r="D6" t="n">
-        <v>1050</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>2305</v>
+        <v>439</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>324</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5272</v>
+        <v>1401</v>
       </c>
       <c r="C2" t="n">
-        <v>8386</v>
+        <v>4849</v>
       </c>
       <c r="D2" t="n">
-        <v>24041</v>
+        <v>15435</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2885</v>
+        <v>1378</v>
       </c>
       <c r="C3" t="n">
-        <v>5447</v>
+        <v>4240</v>
       </c>
       <c r="D3" t="n">
-        <v>12563</v>
+        <v>13797</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2222</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="n">
-        <v>6083</v>
+        <v>7050</v>
       </c>
       <c r="D4" t="n">
-        <v>5972</v>
+        <v>8830</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>690</v>
       </c>
       <c r="C5" t="n">
-        <v>5332</v>
+        <v>5733</v>
       </c>
       <c r="D5" t="n">
-        <v>2570</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1110</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>3792</v>
+        <v>2457</v>
       </c>
       <c r="D6" t="n">
-        <v>1213</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>572</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>2707</v>
+        <v>796</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1717</v>
+        <v>383</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>825</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5928</v>
+        <v>731</v>
       </c>
       <c r="C2" t="n">
-        <v>7397</v>
+        <v>1983</v>
       </c>
       <c r="D2" t="n">
-        <v>24434</v>
+        <v>10394</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>1331</v>
       </c>
       <c r="C3" t="n">
-        <v>5894</v>
+        <v>4300</v>
       </c>
       <c r="D3" t="n">
-        <v>13136</v>
+        <v>13631</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2145</v>
+        <v>1449</v>
       </c>
       <c r="C4" t="n">
-        <v>5623</v>
+        <v>6514</v>
       </c>
       <c r="D4" t="n">
-        <v>6682</v>
+        <v>9557</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1709</v>
+        <v>699</v>
       </c>
       <c r="C5" t="n">
-        <v>5538</v>
+        <v>6750</v>
       </c>
       <c r="D5" t="n">
-        <v>2981</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1230</v>
+        <v>282</v>
       </c>
       <c r="C6" t="n">
-        <v>4342</v>
+        <v>3326</v>
       </c>
       <c r="D6" t="n">
-        <v>1367</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>702</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3115</v>
+        <v>813</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2104</v>
+        <v>439</v>
       </c>
       <c r="D8" t="n">
-        <v>472</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1148</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>518</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>246</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5441</v>
+        <v>560</v>
       </c>
       <c r="C2" t="n">
-        <v>5029</v>
+        <v>4811</v>
       </c>
       <c r="D2" t="n">
-        <v>20177</v>
+        <v>10282</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3798</v>
+        <v>898</v>
       </c>
       <c r="C3" t="n">
-        <v>8867</v>
+        <v>2720</v>
       </c>
       <c r="D3" t="n">
-        <v>14032</v>
+        <v>12179</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1579</v>
+        <v>1238</v>
       </c>
       <c r="C4" t="n">
-        <v>8393</v>
+        <v>5250</v>
       </c>
       <c r="D4" t="n">
-        <v>6422</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1136</v>
+        <v>913</v>
       </c>
       <c r="C5" t="n">
-        <v>4255</v>
+        <v>6554</v>
       </c>
       <c r="D5" t="n">
-        <v>2140</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>648</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
-        <v>3052</v>
+        <v>5000</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2061</v>
+        <v>1961</v>
       </c>
       <c r="D7" t="n">
-        <v>462</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>601</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3361</v>
+        <v>303</v>
       </c>
       <c r="C2" t="n">
-        <v>2818</v>
+        <v>2253</v>
       </c>
       <c r="D2" t="n">
-        <v>14314</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3876</v>
+        <v>673</v>
       </c>
       <c r="C3" t="n">
-        <v>6478</v>
+        <v>3306</v>
       </c>
       <c r="D3" t="n">
-        <v>14059</v>
+        <v>11219</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2109</v>
+        <v>1034</v>
       </c>
       <c r="C4" t="n">
-        <v>8678</v>
+        <v>4077</v>
       </c>
       <c r="D4" t="n">
-        <v>7518</v>
+        <v>10134</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>987</v>
       </c>
       <c r="C5" t="n">
-        <v>6078</v>
+        <v>6168</v>
       </c>
       <c r="D5" t="n">
-        <v>2650</v>
+        <v>5361</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>516</v>
       </c>
       <c r="C6" t="n">
-        <v>3653</v>
+        <v>5771</v>
       </c>
       <c r="D6" t="n">
-        <v>884</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>2483</v>
+        <v>3017</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1452</v>
+        <v>952</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>556</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3569</v>
+        <v>1474</v>
       </c>
       <c r="C2" t="n">
-        <v>8992</v>
+        <v>14873</v>
       </c>
       <c r="D2" t="n">
-        <v>12554</v>
+        <v>18932</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3071</v>
+        <v>436</v>
       </c>
       <c r="C3" t="n">
-        <v>4219</v>
+        <v>2460</v>
       </c>
       <c r="D3" t="n">
-        <v>13263</v>
+        <v>10127</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>778</v>
       </c>
       <c r="C4" t="n">
-        <v>7420</v>
+        <v>3646</v>
       </c>
       <c r="D4" t="n">
-        <v>8356</v>
+        <v>9905</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>918</v>
       </c>
       <c r="C5" t="n">
-        <v>7174</v>
+        <v>5056</v>
       </c>
       <c r="D5" t="n">
-        <v>3317</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>652</v>
       </c>
       <c r="C6" t="n">
-        <v>4747</v>
+        <v>5950</v>
       </c>
       <c r="D6" t="n">
-        <v>1126</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>3010</v>
+        <v>4203</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1879</v>
+        <v>1810</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>894</v>
+        <v>620</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2106</v>
+        <v>978</v>
       </c>
       <c r="C2" t="n">
-        <v>4196</v>
+        <v>7615</v>
       </c>
       <c r="D2" t="n">
-        <v>8762</v>
+        <v>13631</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3078</v>
+        <v>784</v>
       </c>
       <c r="C3" t="n">
-        <v>5694</v>
+        <v>6219</v>
       </c>
       <c r="D3" t="n">
-        <v>12892</v>
+        <v>11614</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2747</v>
+        <v>1231</v>
       </c>
       <c r="C4" t="n">
-        <v>6933</v>
+        <v>5187</v>
       </c>
       <c r="D4" t="n">
-        <v>8958</v>
+        <v>10392</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>670</v>
       </c>
       <c r="C5" t="n">
-        <v>8273</v>
+        <v>7906</v>
       </c>
       <c r="D5" t="n">
-        <v>3514</v>
+        <v>5571</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>748</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>5776</v>
+        <v>5635</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3276</v>
+        <v>1773</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1446</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2302</v>
+        <v>461</v>
       </c>
       <c r="C2" t="n">
-        <v>9110</v>
+        <v>4368</v>
       </c>
       <c r="D2" t="n">
-        <v>13205</v>
+        <v>9399</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2281</v>
+        <v>732</v>
       </c>
       <c r="C3" t="n">
-        <v>4445</v>
+        <v>6140</v>
       </c>
       <c r="D3" t="n">
-        <v>11463</v>
+        <v>11071</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2546</v>
+        <v>851</v>
       </c>
       <c r="C4" t="n">
-        <v>6260</v>
+        <v>5379</v>
       </c>
       <c r="D4" t="n">
-        <v>9327</v>
+        <v>9868</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>643</v>
       </c>
       <c r="C5" t="n">
-        <v>7575</v>
+        <v>5868</v>
       </c>
       <c r="D5" t="n">
-        <v>4277</v>
+        <v>5586</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>954</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>6834</v>
+        <v>5444</v>
       </c>
       <c r="D6" t="n">
-        <v>1423</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>4343</v>
+        <v>2491</v>
       </c>
       <c r="D7" t="n">
-        <v>627</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>2137</v>
+        <v>690</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>716</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>133</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1563</v>
+        <v>813</v>
       </c>
       <c r="C2" t="n">
-        <v>4699</v>
+        <v>6714</v>
       </c>
       <c r="D2" t="n">
-        <v>9987</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>505</v>
       </c>
       <c r="C3" t="n">
-        <v>5711</v>
+        <v>4537</v>
       </c>
       <c r="D3" t="n">
-        <v>11048</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2253</v>
+        <v>698</v>
       </c>
       <c r="C4" t="n">
-        <v>5560</v>
+        <v>5690</v>
       </c>
       <c r="D4" t="n">
-        <v>9420</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1945</v>
+        <v>664</v>
       </c>
       <c r="C5" t="n">
-        <v>7228</v>
+        <v>5483</v>
       </c>
       <c r="D5" t="n">
-        <v>4810</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>7350</v>
+        <v>5656</v>
       </c>
       <c r="D6" t="n">
-        <v>1680</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>5249</v>
+        <v>3990</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2698</v>
+        <v>1543</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>827</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3161</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>12407</v>
+        <v>8930</v>
       </c>
       <c r="D2" t="n">
-        <v>9257</v>
+        <v>9675</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1565</v>
+        <v>533</v>
       </c>
       <c r="C3" t="n">
-        <v>4761</v>
+        <v>4903</v>
       </c>
       <c r="D3" t="n">
-        <v>10213</v>
+        <v>9587</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1887</v>
+        <v>528</v>
       </c>
       <c r="C4" t="n">
-        <v>5454</v>
+        <v>4973</v>
       </c>
       <c r="D4" t="n">
-        <v>9368</v>
+        <v>9536</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1892</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>6389</v>
+        <v>5472</v>
       </c>
       <c r="D5" t="n">
-        <v>5283</v>
+        <v>6536</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1284</v>
+        <v>469</v>
       </c>
       <c r="C6" t="n">
-        <v>7310</v>
+        <v>5514</v>
       </c>
       <c r="D6" t="n">
-        <v>2032</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>6029</v>
+        <v>4772</v>
       </c>
       <c r="D7" t="n">
-        <v>820</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>3596</v>
+        <v>2645</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1458</v>
+        <v>922</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4397</v>
+        <v>3456</v>
       </c>
       <c r="C2" t="n">
-        <v>14041</v>
+        <v>2421</v>
       </c>
       <c r="D2" t="n">
-        <v>7975</v>
+        <v>15975</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2258</v>
+        <v>250</v>
       </c>
       <c r="C2" t="n">
-        <v>7048</v>
+        <v>21069</v>
       </c>
       <c r="D2" t="n">
-        <v>6813</v>
+        <v>15572</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2206</v>
+        <v>387</v>
       </c>
       <c r="C3" t="n">
-        <v>6946</v>
+        <v>5901</v>
       </c>
       <c r="D3" t="n">
-        <v>11026</v>
+        <v>9046</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2708</v>
+        <v>456</v>
       </c>
       <c r="C4" t="n">
-        <v>7701</v>
+        <v>4836</v>
       </c>
       <c r="D4" t="n">
-        <v>9631</v>
+        <v>9162</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1238</v>
+        <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>9901</v>
+        <v>5133</v>
       </c>
       <c r="D5" t="n">
-        <v>4799</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>7341</v>
+        <v>5389</v>
       </c>
       <c r="D6" t="n">
-        <v>1694</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>3524</v>
+        <v>5090</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>1428</v>
+        <v>3519</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>414</v>
+        <v>1588</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>535</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6553</v>
+        <v>2917</v>
       </c>
       <c r="C2" t="n">
-        <v>6822</v>
+        <v>6932</v>
       </c>
       <c r="D2" t="n">
-        <v>9596</v>
+        <v>35001</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1869</v>
+        <v>1143</v>
       </c>
       <c r="C3" t="n">
-        <v>7076</v>
+        <v>956</v>
       </c>
       <c r="D3" t="n">
-        <v>1979</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5068</v>
+        <v>2361</v>
       </c>
       <c r="C2" t="n">
-        <v>4223</v>
+        <v>7386</v>
       </c>
       <c r="D2" t="n">
-        <v>20243</v>
+        <v>27237</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3453</v>
+        <v>1708</v>
       </c>
       <c r="C3" t="n">
-        <v>5978</v>
+        <v>3925</v>
       </c>
       <c r="D3" t="n">
-        <v>3113</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>846</v>
+        <v>555</v>
       </c>
       <c r="C4" t="n">
-        <v>4189</v>
+        <v>644</v>
       </c>
       <c r="D4" t="n">
-        <v>1580</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4328</v>
+        <v>1809</v>
       </c>
       <c r="C2" t="n">
-        <v>5955</v>
+        <v>4666</v>
       </c>
       <c r="D2" t="n">
-        <v>17201</v>
+        <v>25052</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3487</v>
+        <v>1680</v>
       </c>
       <c r="C3" t="n">
-        <v>4369</v>
+        <v>5116</v>
       </c>
       <c r="D3" t="n">
-        <v>5629</v>
+        <v>10831</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1823</v>
+        <v>993</v>
       </c>
       <c r="C4" t="n">
-        <v>5057</v>
+        <v>2614</v>
       </c>
       <c r="D4" t="n">
-        <v>1826</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>401</v>
+        <v>283</v>
       </c>
       <c r="C5" t="n">
-        <v>2386</v>
+        <v>460</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4762</v>
+        <v>2367</v>
       </c>
       <c r="C2" t="n">
-        <v>6839</v>
+        <v>5341</v>
       </c>
       <c r="D2" t="n">
-        <v>17991</v>
+        <v>23036</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3197</v>
+        <v>1439</v>
       </c>
       <c r="C3" t="n">
-        <v>4513</v>
+        <v>4204</v>
       </c>
       <c r="D3" t="n">
-        <v>6991</v>
+        <v>12326</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2220</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="n">
-        <v>4581</v>
+        <v>4000</v>
       </c>
       <c r="D4" t="n">
-        <v>2464</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>910</v>
+        <v>544</v>
       </c>
       <c r="C5" t="n">
-        <v>3721</v>
+        <v>1649</v>
       </c>
       <c r="D5" t="n">
-        <v>1275</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>1337</v>
+        <v>364</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5287</v>
+        <v>2032</v>
       </c>
       <c r="C2" t="n">
-        <v>10558</v>
+        <v>9369</v>
       </c>
       <c r="D2" t="n">
-        <v>15858</v>
+        <v>24669</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2878</v>
+        <v>1546</v>
       </c>
       <c r="C3" t="n">
-        <v>4655</v>
+        <v>4170</v>
       </c>
       <c r="D3" t="n">
-        <v>7687</v>
+        <v>13086</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1683</v>
+        <v>1119</v>
       </c>
       <c r="C4" t="n">
-        <v>3682</v>
+        <v>4028</v>
       </c>
       <c r="D4" t="n">
-        <v>2804</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>804</v>
+        <v>734</v>
       </c>
       <c r="C5" t="n">
-        <v>3036</v>
+        <v>2856</v>
       </c>
       <c r="D5" t="n">
-        <v>1157</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>1685</v>
+        <v>1010</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>533</v>
+        <v>330</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4745</v>
+        <v>3046</v>
       </c>
       <c r="C2" t="n">
-        <v>9653</v>
+        <v>10667</v>
       </c>
       <c r="D2" t="n">
-        <v>17228</v>
+        <v>22875</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3394</v>
+        <v>1455</v>
       </c>
       <c r="C3" t="n">
-        <v>6974</v>
+        <v>5888</v>
       </c>
       <c r="D3" t="n">
-        <v>8493</v>
+        <v>13853</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2002</v>
+        <v>1136</v>
       </c>
       <c r="C4" t="n">
-        <v>4193</v>
+        <v>4017</v>
       </c>
       <c r="D4" t="n">
-        <v>3676</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1110</v>
+        <v>803</v>
       </c>
       <c r="C5" t="n">
-        <v>3351</v>
+        <v>3354</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>2413</v>
+        <v>1903</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1187</v>
+        <v>656</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>392</v>
+        <v>314</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3642</v>
+        <v>2659</v>
       </c>
       <c r="C2" t="n">
-        <v>6749</v>
+        <v>6485</v>
       </c>
       <c r="D2" t="n">
-        <v>27136</v>
+        <v>17883</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3334</v>
+        <v>1984</v>
       </c>
       <c r="C3" t="n">
-        <v>7301</v>
+        <v>9011</v>
       </c>
       <c r="D3" t="n">
-        <v>9279</v>
+        <v>15578</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2320</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
-        <v>5680</v>
+        <v>5765</v>
       </c>
       <c r="D4" t="n">
-        <v>4489</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="5">
@@ -6420,10 +6420,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1355</v>
+        <v>424</v>
       </c>
       <c r="C5" t="n">
-        <v>3742</v>
+        <v>1864</v>
       </c>
       <c r="D5" t="n">
         <v>1800</v>
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>2880</v>
+        <v>642</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1811</v>
+        <v>307</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>796</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
